--- a/Project Outputs for UZ_PER_loopback_tutorial/Rev01/BOM_JLC/BOM_JLC_UZ_PER_loopback_tutorial_[No Variations]_Rev01.xlsx
+++ b/Project Outputs for UZ_PER_loopback_tutorial/Rev01/BOM_JLC/BOM_JLC_UZ_PER_loopback_tutorial_[No Variations]_Rev01.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nina Diringer\AppData\Local\Temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{285F719C-EC62-441D-B2E2-EB793C2ED1AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{97C6E631-761E-476B-B26E-95CD07CAE619}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="390" yWindow="390" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -44,7 +44,7 @@
     <t>270R</t>
   </si>
   <si>
-    <t>4k99</t>
+    <t>4k3</t>
   </si>
   <si>
     <t>MMBT3904</t>
@@ -188,7 +188,7 @@
     <t>C22966</t>
   </si>
   <si>
-    <t>C23046</t>
+    <t>C23159</t>
   </si>
   <si>
     <t>C20526</t>

--- a/Project Outputs for UZ_PER_loopback_tutorial/Rev01/BOM_JLC/BOM_JLC_UZ_PER_loopback_tutorial_[No Variations]_Rev01.xlsx
+++ b/Project Outputs for UZ_PER_loopback_tutorial/Rev01/BOM_JLC/BOM_JLC_UZ_PER_loopback_tutorial_[No Variations]_Rev01.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="25427"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="25629"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nina Diringer\AppData\Local\Temp\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nina Diringer\repos\uz_per_loopback_tutorial\Project Outputs for UZ_PER_loopback_tutorial\Rev01\BOM_JLC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{97C6E631-761E-476B-B26E-95CD07CAE619}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9744CCC-5207-46AE-8BAF-4422E3C13770}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -258,7 +258,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -281,26 +281,49 @@
       </bottom>
       <diagonal/>
     </border>
+    <border diagonalUp="1">
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal style="thin">
+        <color auto="1"/>
+      </diagonal>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -582,16 +605,16 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="79" style="5" customWidth="1"/>
+    <col min="3" max="3" width="36" customWidth="1"/>
     <col min="4" max="4" width="29.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" ht="30" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="4" t="s">
         <v>18</v>
       </c>
       <c r="C1" s="1" t="s">
@@ -601,11 +624,11 @@
         <v>48</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" ht="30" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>19</v>
       </c>
       <c r="C2" s="2" t="s">
@@ -615,7 +638,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="15.95" customHeight="1">
+    <row r="3" spans="1:4" ht="80.099999999999994" customHeight="1">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
@@ -629,11 +652,11 @@
         <v>50</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="15.95" customHeight="1">
+    <row r="4" spans="1:4" ht="80.099999999999994" customHeight="1">
       <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>21</v>
       </c>
       <c r="C4" s="2" t="s">
@@ -643,7 +666,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="15.95" customHeight="1">
+    <row r="5" spans="1:4" ht="80.099999999999994" customHeight="1">
       <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
@@ -657,11 +680,11 @@
         <v>52</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="15.95" customHeight="1">
+    <row r="6" spans="1:4" ht="80.099999999999994" customHeight="1">
       <c r="A6" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="3" t="s">
         <v>23</v>
       </c>
       <c r="C6" s="2" t="s">
@@ -671,7 +694,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="15.95" customHeight="1">
+    <row r="7" spans="1:4" ht="80.099999999999994" customHeight="1">
       <c r="A7" s="2" t="s">
         <v>6</v>
       </c>
@@ -685,11 +708,11 @@
         <v>54</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="15.95" customHeight="1">
+    <row r="8" spans="1:4" ht="50.1" customHeight="1">
       <c r="A8" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="3" t="s">
         <v>25</v>
       </c>
       <c r="C8" s="2" t="s">
@@ -699,7 +722,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="15.95" customHeight="1">
+    <row r="9" spans="1:4" ht="50.1" customHeight="1">
       <c r="A9" s="2" t="s">
         <v>8</v>
       </c>
@@ -713,11 +736,11 @@
         <v>56</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="15.95" customHeight="1">
+    <row r="10" spans="1:4" ht="50.1" customHeight="1">
       <c r="A10" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="3" t="s">
         <v>27</v>
       </c>
       <c r="C10" s="2" t="s">
@@ -727,7 +750,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="15.95" customHeight="1">
+    <row r="11" spans="1:4" ht="50.1" customHeight="1">
       <c r="A11" s="2" t="s">
         <v>10</v>
       </c>
@@ -741,11 +764,11 @@
         <v>58</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="15.95" customHeight="1">
+    <row r="12" spans="1:4" ht="30" customHeight="1">
       <c r="A12" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C12" s="2" t="s">
@@ -755,7 +778,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="15.95" customHeight="1">
+    <row r="13" spans="1:4" ht="30" customHeight="1">
       <c r="A13" s="2" t="s">
         <v>12</v>
       </c>
@@ -769,11 +792,11 @@
         <v>60</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="15.95" customHeight="1">
+    <row r="14" spans="1:4" ht="30" customHeight="1">
       <c r="A14" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C14" s="2" t="s">
@@ -783,7 +806,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="15.95" customHeight="1">
+    <row r="15" spans="1:4" ht="30" customHeight="1">
       <c r="A15" s="2" t="s">
         <v>14</v>
       </c>
@@ -793,21 +816,21 @@
       <c r="C15" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="D15" s="2"/>
-    </row>
-    <row r="16" spans="1:4" ht="15.95" customHeight="1">
+      <c r="D15" s="6"/>
+    </row>
+    <row r="16" spans="1:4" ht="30" customHeight="1">
       <c r="A16" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="B16" s="3" t="s">
         <v>33</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="D16" s="2"/>
-    </row>
-    <row r="17" spans="1:4" ht="15.95" customHeight="1">
+      <c r="D16" s="6"/>
+    </row>
+    <row r="17" spans="1:4" ht="30" customHeight="1">
       <c r="A17" s="2" t="s">
         <v>16</v>
       </c>
@@ -817,21 +840,21 @@
       <c r="C17" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="D17" s="2"/>
-    </row>
-    <row r="18" spans="1:4" ht="15.95" customHeight="1">
+      <c r="D17" s="6"/>
+    </row>
+    <row r="18" spans="1:4" ht="30" customHeight="1">
       <c r="A18" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="B18" s="3" t="s">
         <v>35</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="D18" s="2"/>
-    </row>
-    <row r="19" spans="1:4" ht="17.100000000000001" customHeight="1">
+      <c r="D18" s="6"/>
+    </row>
+    <row r="19" spans="1:4" ht="30" customHeight="1">
       <c r="A19" s="2"/>
       <c r="B19" s="3" t="s">
         <v>36</v>
@@ -839,15 +862,11 @@
       <c r="C19" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="D19" s="2"/>
-    </row>
-    <row r="20" spans="1:4">
-      <c r="A20" s="4"/>
-      <c r="B20" s="4"/>
-      <c r="C20" s="4"/>
-      <c r="D20" s="4"/>
-    </row>
+      <c r="D19" s="6"/>
+    </row>
+    <row r="20" spans="1:4" ht="20.100000000000001" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>